--- a/results/final_0624_summary/emotions_BinaryVector_summary.xlsx
+++ b/results/final_0624_summary/emotions_BinaryVector_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:BE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,80 +456,260 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>example_precision__0.0</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>f1__0.0</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>f1__0.1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>f1__0.2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>f1__0.3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.0</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.1</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.2</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.0</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.1</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.2</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.3</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.3</t>
         </is>
@@ -563,80 +743,260 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>0.6387±0.0147</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.5975±0.0156</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.5204±0.0199</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.4308±0.0227</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.7777±0.0430</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.8220±0.0297</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.8610±0.0331</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.8671±0.0218</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.6722±0.0246</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.6567±0.0194</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.6110±0.0176</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.5468±0.0220</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>0.7675±0.0193</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>0.7288±0.0238</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0.6567±0.0210</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>0.5585±0.0280</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.5775±0.0271</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.5496±0.0200</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.4861±0.0189</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.4100±0.0232</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.6594±0.0277</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.6382±0.0187</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.5970±0.0166</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.5419±0.0207</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.5863±0.0143</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.5345±0.0150</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0.4676±0.0144</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0.4023±0.0187</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.7694±0.0427</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.8069±0.0287</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.8471±0.0279</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.8584±0.0254</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>0.3096±0.0914</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>0.3431±0.0636</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>0.5159±0.0356</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>0.6572±0.0687</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.6758±0.0245</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.6531±0.0184</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.6073±0.0167</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.5491±0.0209</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.5972±0.0155</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.5435±0.0167</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.4720±0.0169</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.4030±0.0197</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.7787±0.0414</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.8184±0.0262</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.8522±0.0269</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.8629±0.0255</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>0.2951±0.0391</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>0.2411±0.0347</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>0.1349±0.0239</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>0.0489±0.0146</t>
         </is>
@@ -670,80 +1030,260 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>0.6310±0.0171</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.5893±0.0158</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.5154±0.0213</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.4300±0.0227</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.7836±0.0470</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.8274±0.0278</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.8696±0.0311</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.8775±0.0183</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.6701±0.0260</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.6544±0.0191</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.6114±0.0188</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.5492±0.0216</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>0.7642±0.0214</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>0.7256±0.0238</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0.6541±0.0198</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>0.5575±0.0285</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.5744±0.0277</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.5462±0.0198</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.4859±0.0222</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.4117±0.0231</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.6581±0.0285</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.6379±0.0180</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.5982±0.0173</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.5439±0.0212</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.5811±0.0154</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.5311±0.0148</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.4658±0.0147</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0.4023±0.0191</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.7753±0.0450</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.8137±0.0264</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.8566±0.0280</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.8675±0.0230</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>0.3250±0.0793</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>0.3609±0.0606</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>0.5294±0.0477</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>0.6694±0.0737</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.6745±0.0263</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6522±0.0179</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6081±0.0173</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.5515±0.0211</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.5915±0.0176</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.5395±0.0168</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.4701±0.0169</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.4033±0.0199</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7851±0.0439</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.8246±0.0240</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.8615±0.0265</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.8728±0.0220</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>0.2883±0.0369</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>0.2327±0.0361</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>0.1340±0.0318</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>0.0497±0.0166</t>
         </is>
@@ -777,80 +1317,260 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>0.6379±0.0146</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.5967±0.0143</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.5191±0.0202</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.4307±0.0223</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.7777±0.0430</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.8201±0.0301</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.8592±0.0342</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.8671±0.0239</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.6718±0.0246</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.6555±0.0185</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.6094±0.0183</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.5468±0.0216</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>0.7675±0.0197</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>0.7282±0.0234</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>0.6554±0.0213</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>0.5583±0.0278</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.5771±0.0271</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.5481±0.0189</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.4840±0.0197</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.4101±0.0228</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.6594±0.0280</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.6374±0.0181</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.5956±0.0172</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.5419±0.0203</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0.5865±0.0143</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>0.5341±0.0140</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0.4666±0.0146</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0.4023±0.0182</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.7694±0.0427</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.8053±0.0289</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.8451±0.0290</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.8585±0.0261</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>0.3064±0.0917</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>0.3392±0.0587</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>0.5155±0.0370</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>0.6583±0.0690</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.6758±0.0248</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.6521±0.0182</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.6058±0.0174</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.5491±0.0204</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.5972±0.0155</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.5429±0.0162</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.4709±0.0171</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.4029±0.0192</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.7787±0.0414</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.8166±0.0270</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.8500±0.0282</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.8630±0.0262</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
         <is>
           <t>0.2951±0.0408</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>0.2386±0.0337</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>0.1332±0.0241</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>0.0489±0.0146</t>
         </is>
@@ -884,80 +1604,260 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>0.6299±0.0165</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.5891±0.0154</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.5151±0.0209</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.4298±0.0222</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.7827±0.0460</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.8266±0.0281</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.8700±0.0311</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.8773±0.0210</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.6693±0.0252</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.6540±0.0190</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.6113±0.0186</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.5490±0.0213</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>0.7636±0.0209</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>0.7254±0.0238</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>0.6541±0.0196</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>0.5572±0.0276</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.5733±0.0269</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.5459±0.0198</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.4857±0.0221</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.4116±0.0230</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.6571±0.0276</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.6376±0.0181</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.5983±0.0171</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.5440±0.0209</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0.5803±0.0147</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>0.5310±0.0146</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0.4658±0.0144</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0.4023±0.0186</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.7741±0.0438</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.8133±0.0267</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.8572±0.0277</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.8679±0.0244</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
         <is>
           <t>0.3250±0.0793</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>0.3609±0.0606</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>0.5294±0.0477</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>0.6706±0.0740</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.6737±0.0256</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.6519±0.0179</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.6082±0.0170</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.5513±0.0207</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.5908±0.0168</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.5394±0.0167</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.4701±0.0165</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.4031±0.0194</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0.7841±0.0431</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.8242±0.0244</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.8620±0.0264</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.8729±0.0236</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
         <is>
           <t>0.2866±0.0370</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>0.2327±0.0361</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>0.1332±0.0321</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>0.0497±0.0166</t>
         </is>
@@ -991,80 +1891,260 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>0.6747±0.0137</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.6829±0.0183</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.6440±0.0260</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.5906±0.0275</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.7133±0.0367</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.7247±0.0314</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.7085±0.0292</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.6827±0.0341</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.6622±0.0208</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.6697±0.0164</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.6408±0.0205</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.5995±0.0233</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>0.7830±0.0173</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>0.7834±0.0122</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>0.7611±0.0171</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>0.7257±0.0216</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.5760±0.0232</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.5786±0.0189</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.5434±0.0211</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.4928±0.0253</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.6491±0.0305</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.6515±0.0214</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.6261±0.0237</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.5875±0.0302</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0.6176±0.0190</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>0.6205±0.0159</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0.5912±0.0288</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0.5398±0.0349</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.6993±0.0412</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.7015±0.0383</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.6894±0.0333</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.6628±0.0306</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
         <is>
           <t>0.4376±0.1117</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>0.4074±0.0987</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>0.4551±0.0872</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>0.3833±0.0973</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.6712±0.0270</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.6727±0.0188</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.6466±0.0210</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.6054±0.0280</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.6349±0.0193</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.6354±0.0167</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.6002±0.0279</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.5491±0.0323</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.7126±0.0404</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.7160±0.0374</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.7021±0.0279</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.6759±0.0340</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
         <is>
           <t>0.3238±0.0289</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>0.3136±0.0313</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>0.2589±0.0321</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>0.1881±0.0402</t>
         </is>
@@ -1098,80 +2178,260 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>0.6523±0.0100</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.6424±0.0080</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.5932±0.0208</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.5179±0.0173</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.7628±0.0324</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.7801±0.0251</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.8034±0.0230</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.7820±0.0239</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.6729±0.0160</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.6742±0.0121</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.6528±0.0183</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.5943±0.0183</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>0.7771±0.0129</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>0.7736±0.0120</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>0.7432±0.0140</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>0.6807±0.0185</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.5814±0.0210</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.5763±0.0164</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.5427±0.0196</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.4724±0.0195</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.6598±0.0228</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.6628±0.0175</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.6456±0.0191</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.5900±0.0217</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0.5992±0.0111</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>0.5941±0.0128</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0.5542±0.0189</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0.4862±0.0237</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.7474±0.0346</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.7608±0.0269</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.7893±0.0280</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.7677±0.0194</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
         <is>
           <t>0.3568±0.1144</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>0.3214±0.0477</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>0.3744±0.0838</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>0.3554±0.0766</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.6799±0.0198</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.6808±0.0149</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.6598±0.0185</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.6027±0.0214</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.6147±0.0128</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.6067±0.0113</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.5616±0.0193</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.4922±0.0229</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.7611±0.0355</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.7759±0.0261</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.8000±0.0245</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.7780±0.0221</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
         <is>
           <t>0.3103±0.0434</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>0.2841±0.0391</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>0.2124±0.0324</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>0.1146±0.0185</t>
         </is>
@@ -1205,80 +2465,260 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>0.6871±0.0189</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.6858±0.0163</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.6483±0.0272</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.5970±0.0287</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.6874±0.0347</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.6928±0.0297</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.6804±0.0294</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.6614±0.0364</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.6553±0.0171</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.6548±0.0166</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.6283±0.0191</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.5919±0.0234</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>0.7819±0.0158</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>0.7775±0.0149</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>0.7574±0.0135</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>0.7249±0.0215</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.5693±0.0164</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.5628±0.0206</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.5303±0.0195</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.4856±0.0239</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.6410±0.0281</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0.6375±0.0209</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0.6124±0.0220</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0.5786±0.0300</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0.6230±0.0218</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>0.6202±0.0133</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0.5911±0.0277</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0.5414±0.0361</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.6722±0.0384</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.6710±0.0357</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.6586±0.0337</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.6400±0.0312</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
         <is>
           <t>0.4311±0.0981</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>0.4317±0.0786</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>0.4621±0.0968</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>0.3931±0.0950</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.6607±0.0246</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.6561±0.0197</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.6323±0.0182</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.5960±0.0273</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.6405±0.0193</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.6328±0.0155</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.5996±0.0262</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.5501±0.0331</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.6830±0.0383</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.6821±0.0358</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.6705±0.0300</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.6517±0.0343</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
         <is>
           <t>0.3204±0.0187</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>0.2918±0.0334</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
         <is>
           <t>0.2445±0.0228</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>0.1872±0.0308</t>
         </is>
@@ -1312,80 +2752,260 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>0.6516±0.0094</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.6419±0.0084</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.5943±0.0204</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.5147±0.0155</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.7634±0.0320</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.7812±0.0236</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.8066±0.0200</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.7812±0.0206</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.6725±0.0152</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.6746±0.0117</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.6543±0.0168</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.5925±0.0155</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>0.7765±0.0154</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>0.7739±0.0117</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>0.7438±0.0123</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>0.6790±0.0158</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.5812±0.0187</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.5772±0.0150</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.5441±0.0189</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.4700±0.0176</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.6598±0.0241</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.6637±0.0168</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.6470±0.0173</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.5884±0.0186</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0.5982±0.0150</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>0.5942±0.0124</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0.5544±0.0180</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0.4845±0.0214</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.7481±0.0349</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.7626±0.0260</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.7920±0.0258</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.7672±0.0159</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
         <is>
           <t>0.3489±0.1135</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>0.3235±0.0456</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>0.3713±0.0891</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>0.3606±0.0764</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.6797±0.0206</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.6816±0.0145</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.6610±0.0171</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.6015±0.0184</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.6138±0.0149</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.6069±0.0116</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.5621±0.0186</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.4905±0.0206</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.7621±0.0349</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.7776±0.0250</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.8027±0.0223</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.7780±0.0185</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
         <is>
           <t>0.3103±0.0390</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>0.2875±0.0339</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="BD9" t="inlineStr">
         <is>
           <t>0.2149±0.0327</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>0.1079±0.0170</t>
         </is>
@@ -1419,80 +3039,260 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>0.6756±0.0260</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.6767±0.0212</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.6338±0.0274</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.5643±0.0252</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.6217±0.0234</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.6229±0.0354</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.5983±0.0404</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.5606±0.0532</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>0.6194±0.0250</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>0.6170±0.0242</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>0.5853±0.0313</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>0.5274±0.0292</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>0.8198±0.0133</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>0.8121±0.0103</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>0.7910±0.0095</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>0.7496±0.0142</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0.5475±0.0278</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0.5361±0.0250</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0.5046±0.0313</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0.4389±0.0283</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.6525±0.0317</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0.6454±0.0287</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.6155±0.0203</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0.5669±0.0302</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0.7676±0.0278</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>0.7343±0.0232</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0.6740±0.0251</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0.6007±0.0327</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0.6030±0.0333</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0.5999±0.0364</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>0.5879±0.0313</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>0.5559±0.0516</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
         <is>
           <t>0.6978±0.0896</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>0.6294±0.0952</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>0.6414±0.0810</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>0.5358±0.1301</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>0.6824±0.0295</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.6716±0.0192</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.6426±0.0230</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.5823±0.0273</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>0.7545±0.0279</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>0.7369±0.0212</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>0.6873±0.0281</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.6074±0.0284</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0.6234±0.0345</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0.6182±0.0334</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>0.6050±0.0362</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>0.5631±0.0546</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
         <is>
           <t>0.3305±0.0367</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>0.2900±0.0338</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="BD10" t="inlineStr">
         <is>
           <t>0.2598±0.0387</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>0.1805±0.0345</t>
         </is>
@@ -1526,80 +3326,260 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>0.6863±0.0297</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.6814±0.0132</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.6320±0.0327</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.5465±0.0419</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.6248±0.0123</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.6309±0.0236</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.5824±0.0490</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.5464±0.0459</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>0.6239±0.0200</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>0.6247±0.0130</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>0.5744±0.0393</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>0.5128±0.0365</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>0.8139±0.0120</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>0.8114±0.0085</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>0.7926±0.0145</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>0.7460±0.0149</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0.5467±0.0235</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.5477±0.0155</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0.4938±0.0374</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0.4259±0.0296</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0.6406±0.0294</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0.6467±0.0226</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.6076±0.0375</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0.5550±0.0278</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>0.7471±0.0318</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>0.7347±0.0322</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>0.6961±0.0224</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>0.5953±0.0390</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>0.6011±0.0288</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0.6088±0.0288</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>0.5616±0.0502</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>0.5351±0.0389</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
         <is>
           <t>0.7331±0.0681</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>0.6661±0.0752</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>0.6542±0.0830</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>0.5322±0.0867</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>0.6762±0.0262</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.6745±0.0143</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.6344±0.0323</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>0.5721±0.0272</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>0.7367±0.0310</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>0.7294±0.0225</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>0.7022±0.0218</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>0.6028±0.0349</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>0.6253±0.0265</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>0.6280±0.0231</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>0.5802±0.0485</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>0.5464±0.0384</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
         <is>
           <t>0.3153±0.0420</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>0.3128±0.0264</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="BD11" t="inlineStr">
         <is>
           <t>0.2487±0.0392</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>0.1703±0.0193</t>
         </is>
@@ -1633,82 +3613,1123 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>0.3969±0.0259</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.4109±0.0525</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.4113±0.0504</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.3595±0.0526</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.2811±0.0171</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.3050±0.0381</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0.3036±0.0419</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.2598±0.0365</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>0.3154±0.0191</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>0.3344±0.0410</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>0.3308±0.0400</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>0.2873±0.0409</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>0.7606±0.0059</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>0.7635±0.0124</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>0.7594±0.0152</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>0.7451±0.0144</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0.2701±0.0186</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0.2863±0.0374</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0.2802±0.0368</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0.2424±0.0348</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>0.3928±0.0133</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>0.4175±0.0425</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>0.4135±0.0519</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>0.3540±0.0560</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>0.8437±0.0271</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>0.8143±0.0633</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>0.7595±0.0777</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>0.7223±0.1042</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>0.2800±0.0151</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>0.3029±0.0352</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>0.3046±0.0499</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>0.2482±0.0474</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
         <is>
           <t>0.9395±0.0277</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>0.9318±0.0338</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>0.9347±0.0510</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
         <is>
           <t>0.9353±0.0592</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>0.4313±0.0259</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.4518±0.0447</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.4451±0.0451</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>0.3860±0.0534</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>0.8262±0.0357</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>0.8085±0.0467</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>0.7912±0.0526</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>0.7662±0.0525</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>0.2922±0.0223</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>0.3147±0.0383</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>0.3119±0.0422</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>0.2594±0.0444</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
         <is>
           <t>0.1333±0.0167</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>0.1392±0.0377</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="BD12" t="inlineStr">
         <is>
           <t>0.1299±0.0356</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>0.1096±0.0209</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ecc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.3112±0.0239</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.3180±0.0395</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.2915±0.0352</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.2811±0.0413</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.6877±0.0177</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.6746±0.0227</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.6473±0.0305</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.5916±0.0395</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.6475±0.0215</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.6252±0.0245</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.6251±0.0367</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.5926±0.0394</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.6381±0.0161</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.6191±0.0236</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.6027±0.0284</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.5570±0.0315</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0.8184±0.0106</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0.8138±0.0122</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>0.7970±0.0123</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>0.7649±0.0157</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0.5646±0.0210</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0.5432±0.0308</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0.5198±0.0291</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>0.4705±0.0296</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>0.6604±0.0255</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>0.6413±0.0354</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>0.6291±0.0328</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0.5878±0.0328</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>0.7450±0.0254</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>0.7456±0.0375</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>0.6794±0.0344</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>0.6245±0.0247</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>0.6215±0.0295</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>0.6013±0.0387</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>0.6076±0.0371</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0.5744±0.0444</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>0.6343±0.0558</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>0.7176±0.0683</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>0.6284±0.0903</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>0.5617±0.1229</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>0.6881±0.0227</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>0.6754±0.0267</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0.6565±0.0292</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>0.6068±0.0322</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>0.7387±0.0240</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>0.7379±0.0331</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>0.6924±0.0282</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>0.6322±0.0277</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>0.6445±0.0282</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>0.6235±0.0323</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>0.6252±0.0383</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>0.5846±0.0437</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>0.3389±0.0415</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>0.3128±0.0505</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.2682±0.0346</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.2091±0.0330</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>lp</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.1820±0.0281</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.2170±0.0182</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.2742±0.0477</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.2197±0.0403</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.6866±0.0233</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.6660±0.0269</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.5688±0.0332</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.4902±0.0397</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.7203±0.0369</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.6726±0.0372</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0.5865±0.0439</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0.5583±0.0319</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.6777±0.0262</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.6414±0.0302</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.5465±0.0250</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.4864±0.0314</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0.8072±0.0167</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0.7886±0.0181</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>0.7411±0.0116</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>0.6859±0.0221</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0.5987±0.0277</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0.5593±0.0316</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>0.4576±0.0254</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0.3908±0.0316</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>0.6867±0.0336</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>0.6481±0.0341</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>0.5646±0.0231</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>0.5074±0.0288</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>0.6760±0.0283</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>0.6544±0.0410</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>0.5769±0.0306</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>0.4864±0.0308</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>0.7123±0.0402</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>0.6531±0.0348</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>0.5721±0.0484</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>0.5397±0.0348</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>0.3597±0.1001</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>0.4153±0.0863</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>0.5263±0.0761</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>0.4324±0.0895</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>0.6997±0.0287</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>0.6620±0.0293</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>0.5852±0.0218</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>0.5214±0.0274</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>0.6785±0.0267</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>0.6594±0.0312</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>0.5853±0.0295</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>0.4967±0.0296</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>0.7231±0.0390</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>0.6655±0.0358</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>0.5881±0.0429</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>0.5495±0.0317</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>0.3659±0.0366</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>0.3178±0.0384</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.2007±0.0325</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.1231±0.0350</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mlknn</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.4666±0.0555</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.4282±0.0654</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.4052±0.0597</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.2922±0.0694</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.5041±0.0494</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.4989±0.0334</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.4575±0.0352</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.4321±0.0317</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.4252±0.0403</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0.4524±0.0380</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0.4366±0.0429</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0.4804±0.0546</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.4347±0.0379</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0.4456±0.0226</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0.4185±0.0320</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0.4198±0.0357</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0.7276±0.0106</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0.7142±0.0087</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>0.6880±0.0140</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>0.6484±0.0224</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0.3644±0.0287</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0.3642±0.0205</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>0.3365±0.0269</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0.3243±0.0312</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>0.4299±0.0363</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>0.4435±0.0303</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>0.4253±0.0310</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>0.4309±0.0376</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>0.5469±0.0631</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>0.5050±0.0235</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>0.4719±0.0327</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>0.4255±0.0350</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>0.3987±0.0477</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>0.4261±0.0421</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>0.4184±0.0564</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>0.4610±0.0585</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>0.9275±0.0419</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>0.7903±0.1128</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>0.7447±0.0952</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>0.5943±0.1523</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>0.4921±0.0335</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>0.4941±0.0239</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>0.4657±0.0325</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>0.4551±0.0360</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>0.5856±0.0286</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>0.5515±0.0335</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>0.4991±0.0296</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>0.4413±0.0349</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>0.4255±0.0393</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>0.4496±0.0351</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>0.4387±0.0462</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>0.4741±0.0584</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>0.1619±0.0303</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>0.1374±0.0203</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.1138±0.0260</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.0733±0.0225</t>
         </is>
       </c>
     </row>
